--- a/research/runs/20260302-070309-excel-formula-language-pass2-pack-01/fixtures/formula_parse_pass2/FMLP2-001.xlsx
+++ b/research/runs/20260302-070309-excel-formula-language-pass2-pack-01/fixtures/formula_parse_pass2/FMLP2-001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\DnaCalc\Foundation\research\runs\20260302-070309-excel-formula-language-pass2-pack-01\fixtures\formula_parse_pass2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07F1B09-BB6C-404C-AB44-E4079B702B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D4C5CE-B743-42F4-B784-DB415FFFA5B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3135" yWindow="3885" windowWidth="11955" windowHeight="11595" xr2:uid="{A42862BF-252B-48CD-94FE-068EA09FD0F5}"/>
   </bookViews>
